--- a/incident_report_forms/031_fire_drill_coordination_request_form--incident_report_forms.xlsx
+++ b/incident_report_forms/031_fire_drill_coordination_request_form--incident_report_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -803,8 +803,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -832,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'central_office',_'label':_'central_office'}</t>
+          <t>central_office</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Central Office', 'label': 'Central Office'}</t>
+          <t>Central Office</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'main_building',_'label':_'main_building'}</t>
+          <t>main_building</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Main Building', 'label': 'Main Building'}</t>
+          <t>Main Building</t>
         </is>
       </c>
     </row>
@@ -866,12 +866,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'training_room',_'label':_'training_room'}</t>
+          <t>training_room</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Training Room', 'label': 'Training Room'}</t>
+          <t>Training Room</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'fire_alarm',_'label':_'fire_alarm'}</t>
+          <t>fire_alarm</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Fire Alarm', 'label': 'Fire Alarm'}</t>
+          <t>Fire Alarm</t>
         </is>
       </c>
     </row>
@@ -900,12 +900,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'emergency_response',_'label':_'emergency_response'}</t>
+          <t>emergency_response</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Emergency Response', 'label': 'Emergency Response'}</t>
+          <t>Emergency Response</t>
         </is>
       </c>
     </row>
@@ -917,12 +917,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'evacuation',_'label':_'evacuation'}</t>
+          <t>evacuation</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Evacuation', 'label': 'Evacuation'}</t>
+          <t>Evacuation</t>
         </is>
       </c>
     </row>
